--- a/原始数据/新质生产力测度指标/获得机器设备和软件经费支出占比%.xlsx
+++ b/原始数据/新质生产力测度指标/获得机器设备和软件经费支出占比%.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xya\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tjjmlinxieli\原始数据\新质生产力测度指标\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40B142EA-61F8-4A8F-B28D-212655973C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18647296-6B34-48D2-984E-536895D4975F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10700" yWindow="4400" windowWidth="18540" windowHeight="10310" xr2:uid="{C2F878A4-5B58-400C-97FF-4242AC171924}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="15196" xr2:uid="{C2F878A4-5B58-400C-97FF-4242AC171924}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -488,14 +488,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21B8D62-6209-49D2-B4BC-EA3F5BB93DA3}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B1">
         <v>2016</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C1">
+        <v>2017</v>
+      </c>
+      <c r="D1">
+        <v>2018</v>
+      </c>
+      <c r="E1">
+        <v>2019</v>
+      </c>
+      <c r="F1">
+        <v>2020</v>
+      </c>
+      <c r="G1">
+        <v>2021</v>
+      </c>
+      <c r="H1">
+        <v>2022</v>
+      </c>
+      <c r="I1">
+        <v>2023</v>
+      </c>
+      <c r="J1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -527,7 +551,7 @@
         <v>28.76</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -559,7 +583,7 @@
         <v>14.56</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -591,7 +615,7 @@
         <v>28.31</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -623,7 +647,7 @@
         <v>35.979999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -655,7 +679,7 @@
         <v>41.02</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -687,7 +711,7 @@
         <v>30.27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -719,7 +743,7 @@
         <v>59.95</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -751,7 +775,7 @@
         <v>32.479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -783,7 +807,7 @@
         <v>29.29</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -815,7 +839,7 @@
         <v>21.43</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -847,7 +871,7 @@
         <v>33.549999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -879,7 +903,7 @@
         <v>28.17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -911,7 +935,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -943,7 +967,7 @@
         <v>34.25</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -975,7 +999,7 @@
         <v>27.33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1007,7 +1031,7 @@
         <v>15.02</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1039,7 +1063,7 @@
         <v>28.42</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1071,7 +1095,7 @@
         <v>24.62</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1103,7 +1127,7 @@
         <v>32.880000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1135,7 +1159,7 @@
         <v>54.11</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -1167,7 +1191,7 @@
         <v>39.770000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1199,7 +1223,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1231,7 +1255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1263,7 +1287,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1295,7 +1319,7 @@
         <v>23.61</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1327,7 +1351,7 @@
         <v>25.51</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1359,7 +1383,7 @@
         <v>54.38</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1391,7 +1415,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1423,7 +1447,7 @@
         <v>49.67</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>29</v>
       </c>
